--- a/correctionProfile/ig/StructureDefinition-fr-observation-result-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-result-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3004" uniqueCount="542">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -722,7 +722,7 @@
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">type:$this}
 </t>
   </si>
   <si>
@@ -741,11 +741,125 @@
     <t>serviceRequestAccessionNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-imaging-document|0.1.0)
 </t>
   </si>
   <si>
     <t>Référence à la demande d'examen contenant l'Accession Number</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.id</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.id</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.extension</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.reference</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.type</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.identifier</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-accession-number-identifier-document|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Observation.basedOn:serviceRequestAccessionNumber.display</t>
+  </si>
+  <si>
+    <t>Observation.basedOn.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>Observation.partOf</t>
@@ -1113,9 +1227,6 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -1332,12 +1443,6 @@
   </si>
   <si>
     <t>Observation.referenceRange.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1924,10 +2029,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP72"/>
+  <dimension ref="A1:AP78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.80859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.86328125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.09765625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -5913,18 +6018,18 @@
         <v>234</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5933,20 +6038,18 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>236</v>
+        <v>153</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5995,31 +6098,31 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>157</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6028,48 +6131,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6078,7 +6179,7 @@
         <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>82</v>
@@ -6093,58 +6194,58 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>243</v>
+        <v>162</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>254</v>
+        <v>157</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6152,10 +6253,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6166,7 +6267,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6175,23 +6276,21 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6215,13 +6314,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>262</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6239,16 +6338,16 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>105</v>
@@ -6263,35 +6362,35 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>263</v>
+        <v>136</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6300,20 +6399,18 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6337,13 +6434,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6361,10 +6458,10 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>93</v>
@@ -6376,30 +6473,30 @@
         <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>275</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>277</v>
+        <v>136</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6413,7 +6510,7 @@
         <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6422,20 +6519,18 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6483,7 +6578,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6498,19 +6593,19 @@
         <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6518,10 +6613,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6532,7 +6627,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6544,16 +6639,16 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>291</v>
+        <v>153</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6603,13 +6698,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6624,13 +6719,13 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>295</v>
+        <v>136</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6638,21 +6733,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6664,20 +6759,18 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6725,13 +6818,13 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -6740,19 +6833,19 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6760,14 +6853,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6780,25 +6873,25 @@
         <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>309</v>
+        <v>113</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6808,7 +6901,7 @@
         <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>82</v>
@@ -6823,13 +6916,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -6847,10 +6940,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>93</v>
@@ -6862,19 +6955,19 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>314</v>
+        <v>287</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6882,10 +6975,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6896,7 +6989,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6905,21 +6998,23 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>319</v>
+        <v>190</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -6943,13 +7038,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6967,13 +7062,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -6988,38 +7083,38 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
@@ -7028,17 +7123,19 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>327</v>
+        <v>190</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7063,13 +7160,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7087,13 +7184,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7102,30 +7199,30 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7148,19 +7245,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7209,7 +7306,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7218,36 +7315,36 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7258,7 +7355,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7267,23 +7364,21 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>190</v>
+        <v>327</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7307,13 +7402,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7331,16 +7426,16 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>105</v>
@@ -7352,28 +7447,28 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>136</v>
+        <v>312</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7383,28 +7478,28 @@
         <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K46" t="s" s="2">
-        <v>190</v>
+        <v>334</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7429,11 +7524,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7451,13 +7548,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -7466,41 +7563,41 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>94</v>
@@ -7509,22 +7606,22 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7573,13 +7670,13 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -7588,30 +7685,30 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7625,25 +7722,25 @@
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K48" t="s" s="2">
-        <v>190</v>
+        <v>355</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7669,13 +7766,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7693,7 +7790,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>375</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7711,27 +7808,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7742,31 +7839,29 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>190</v>
+        <v>363</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7791,11 +7886,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7813,13 +7910,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7828,30 +7925,30 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7859,33 +7956,35 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>396</v>
+        <v>374</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7933,7 +8032,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7942,7 +8041,7 @@
         <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -7951,27 +8050,27 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>401</v>
+        <v>381</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7994,18 +8093,20 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>403</v>
+        <v>190</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8029,13 +8130,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8053,7 +8154,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8062,7 +8163,7 @@
         <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>105</v>
@@ -8071,38 +8172,38 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>408</v>
+        <v>136</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>94</v>
@@ -8114,19 +8215,19 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>412</v>
+        <v>190</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8151,13 +8252,11 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8175,7 +8274,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8187,33 +8286,33 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8224,10 +8323,10 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8236,16 +8335,20 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>153</v>
+        <v>403</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>154</v>
+        <v>404</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8293,19 +8396,19 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>156</v>
+        <v>402</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8314,10 +8417,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>157</v>
+        <v>409</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8326,26 +8429,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -8354,16 +8457,16 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>208</v>
+        <v>413</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8389,13 +8492,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8413,80 +8516,80 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>157</v>
+        <v>418</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>208</v>
+        <v>423</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>209</v>
+        <v>424</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8511,13 +8614,11 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8535,19 +8636,19 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8556,10 +8657,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>136</v>
+        <v>427</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8570,10 +8671,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8596,15 +8697,17 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8653,7 +8756,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8662,7 +8765,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -8671,7 +8774,7 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>434</v>
@@ -8683,15 +8786,15 @@
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8714,15 +8817,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8771,7 +8876,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8780,7 +8885,7 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>105</v>
@@ -8789,27 +8894,27 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8820,10 +8925,10 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -8832,19 +8937,19 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>190</v>
+        <v>447</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8869,55 +8974,55 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AA58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>452</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>365</v>
+        <v>454</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -8928,10 +9033,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8942,7 +9047,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -8954,20 +9059,16 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>450</v>
+        <v>154</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -8991,13 +9092,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9015,31 +9116,31 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>449</v>
+        <v>156</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>365</v>
+        <v>157</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9057,14 +9158,14 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9076,18 +9177,18 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>457</v>
+        <v>138</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>238</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9135,19 +9236,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>162</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9159,7 +9260,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>461</v>
+        <v>157</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9170,42 +9271,46 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9253,19 +9358,19 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9274,10 +9379,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>465</v>
+        <v>136</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9288,10 +9393,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9302,7 +9407,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9311,20 +9416,18 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9373,16 +9476,16 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI62" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>105</v>
@@ -9394,10 +9497,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9408,10 +9511,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9422,7 +9525,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9431,20 +9534,18 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9493,16 +9594,16 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>105</v>
@@ -9514,10 +9615,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9528,10 +9629,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9542,7 +9643,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9551,22 +9652,22 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>412</v>
+        <v>190</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9591,13 +9692,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9615,13 +9716,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9633,13 +9734,13 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>485</v>
+        <v>400</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9650,10 +9751,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9664,7 +9765,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9676,16 +9777,20 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>154</v>
+        <v>483</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -9709,13 +9814,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -9733,31 +9838,31 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>156</v>
+        <v>482</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>157</v>
+        <v>400</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9768,21 +9873,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -9794,18 +9899,18 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>138</v>
+        <v>490</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>422</v>
+        <v>491</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -9853,19 +9958,19 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>162</v>
+        <v>489</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
@@ -9877,7 +9982,7 @@
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>157</v>
+        <v>494</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -9888,46 +9993,42 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>426</v>
+        <v>496</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -9975,19 +10076,19 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>428</v>
+        <v>495</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -9996,10 +10097,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>136</v>
+        <v>498</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10010,10 +10111,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10021,10 +10122,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10036,20 +10137,18 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10073,13 +10172,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10097,13 +10196,13 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
@@ -10115,16 +10214,16 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>276</v>
+        <v>504</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>277</v>
+        <v>505</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>82</v>
@@ -10132,10 +10231,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10146,7 +10245,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10158,20 +10257,18 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>336</v>
+        <v>507</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>338</v>
+        <v>509</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10219,13 +10316,13 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
@@ -10237,27 +10334,27 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>343</v>
+        <v>504</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>344</v>
+        <v>511</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10268,7 +10365,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10277,22 +10374,22 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>190</v>
+        <v>447</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>350</v>
+        <v>516</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10317,13 +10414,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10341,16 +10438,16 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>105</v>
@@ -10362,10 +10459,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>136</v>
+        <v>517</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>355</v>
+        <v>518</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10376,21 +10473,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10402,20 +10499,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>503</v>
+        <v>154</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10439,13 +10532,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>504</v>
+        <v>82</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10463,49 +10556,49 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>502</v>
+        <v>156</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>365</v>
+        <v>157</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10524,20 +10617,18 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>507</v>
+        <v>238</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>508</v>
+        <v>239</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -10585,7 +10676,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>506</v>
+        <v>162</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10597,29 +10688,761 @@
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AK72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP72" t="s" s="2">
+      <c r="AK74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP72">
+  <autoFilter ref="A1:AP78">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10629,7 +11452,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI71">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-result-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-result-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-result-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-result-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1259,7 +1259,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260716085852</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260916095455</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1345,7 +1345,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260916095453</t>
   </si>
   <si>
     <t>OBX-17</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-result-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-result-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-observation-result-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-observation-result-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
